--- a/cet4/result/62_穿越女帝_公主权谋天下路/62_穿越女帝_公主权谋天下路_学习版.xlsx
+++ b/cet4/result/62_穿越女帝_公主权谋天下路/62_穿越女帝_公主权谋天下路_学习版.xlsx
@@ -397,801 +397,661 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D46"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>cherry</v>
       </c>
       <c r="B2" t="str">
-        <v>cherry</v>
+        <v>/ˈtʃeri/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>樱桃</v>
       </c>
-      <c r="D2" t="str">
-        <v>cherry(樱桃)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>grind</v>
       </c>
       <c r="B3" t="str">
-        <v>grind</v>
+        <v>/ɡraɪnd/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>磨碎</v>
       </c>
-      <c r="D3" t="str">
-        <v>grind(磨碎)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>relativity</v>
       </c>
       <c r="B4" t="str">
-        <v>relativity</v>
+        <v>/ˌreləˈtɪvəti/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>相对论</v>
       </c>
-      <c r="D4" t="str">
-        <v>relativity(相对论)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>undoubtedly</v>
       </c>
       <c r="B5" t="str">
-        <v>undoubtedly</v>
+        <v>/ʌnˈdaʊtɪdli/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>确实地</v>
       </c>
-      <c r="D5" t="str">
-        <v>undoubtedly(确实地)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>clothing</v>
       </c>
       <c r="B6" t="str">
-        <v>clothing</v>
+        <v>/ˈkloʊðɪŋ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D6" t="str">
         <v>服装</v>
       </c>
-      <c r="D6" t="str">
-        <v>clothing(服装)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>become</v>
       </c>
       <c r="B7" t="str">
-        <v>become</v>
+        <v>/bɪˈkʌm/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>成为</v>
       </c>
-      <c r="D7" t="str">
-        <v>become(成为)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>princess</v>
       </c>
       <c r="B8" t="str">
-        <v>princess</v>
+        <v>/ˈprɪnses/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>公主</v>
       </c>
-      <c r="D8" t="str">
-        <v>princess(公主)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>childhood</v>
       </c>
       <c r="B9" t="str">
-        <v>childhood</v>
+        <v>/ˈtʃaɪldhʊd/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>童年</v>
       </c>
-      <c r="D9" t="str">
-        <v>childhood(童年)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>orphan</v>
       </c>
       <c r="B10" t="str">
-        <v>orphan</v>
+        <v>/ˈɔːrfn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>孤儿</v>
       </c>
-      <c r="D10" t="str">
-        <v>orphan(孤儿)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>humble</v>
       </c>
       <c r="B11" t="str">
-        <v>humble</v>
+        <v>/ˈhʌmbl/</v>
       </c>
       <c r="C11" t="str">
+        <v>vt./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>谦逊的</v>
       </c>
-      <c r="D11" t="str">
-        <v>humble(谦逊的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>genius</v>
       </c>
       <c r="B12" t="str">
-        <v>genius</v>
+        <v>/ˈdʒiːniəs/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>天才</v>
       </c>
-      <c r="D12" t="str">
-        <v>genius(天才)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>piano</v>
       </c>
       <c r="B13" t="str">
-        <v>piano</v>
+        <v>/piˈænoʊ/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>钢琴</v>
       </c>
-      <c r="D13" t="str">
-        <v>piano(钢琴)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>soccer</v>
       </c>
       <c r="B14" t="str">
-        <v>soccer</v>
+        <v>/ˈsɑːkər/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>足球</v>
       </c>
-      <c r="D14" t="str">
-        <v>soccer(足球)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>fever</v>
       </c>
       <c r="B15" t="str">
-        <v>fever</v>
+        <v>/ˈfiːvər/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>发烧</v>
       </c>
-      <c r="D15" t="str">
-        <v>fever(发烧)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>harmful</v>
       </c>
       <c r="B16" t="str">
-        <v>harmful</v>
+        <v>/ˈhɑːrmfl/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>有害的</v>
       </c>
-      <c r="D16" t="str">
-        <v>harmful(有害的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>angry</v>
       </c>
       <c r="B17" t="str">
-        <v>angry</v>
+        <v>/ˈæŋɡri/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>生气的</v>
       </c>
-      <c r="D17" t="str">
-        <v>angry(生气的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>thief</v>
       </c>
       <c r="B18" t="str">
-        <v>thief</v>
+        <v>/θiːf/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>小偷</v>
       </c>
-      <c r="D18" t="str">
-        <v>thief(小偷)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>slow</v>
       </c>
       <c r="B19" t="str">
-        <v>slow</v>
+        <v>/sloʊ/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D19" t="str">
         <v>慢的</v>
       </c>
-      <c r="D19" t="str">
-        <v>slow(慢的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>acre</v>
       </c>
       <c r="B20" t="str">
-        <v>acre</v>
+        <v>/ˈeɪkər/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>英亩</v>
       </c>
-      <c r="D20" t="str">
-        <v>acre(英亩)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>middle</v>
       </c>
       <c r="B21" t="str">
-        <v>middle</v>
+        <v>/ˈmɪdl/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>中间</v>
       </c>
-      <c r="D21" t="str">
-        <v>middle(中间)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>institution</v>
       </c>
       <c r="B22" t="str">
-        <v>institution</v>
+        <v>/ˌɪnstɪˈtuːʃn/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>制度</v>
       </c>
-      <c r="D22" t="str">
-        <v>institution(制度)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>administration</v>
       </c>
       <c r="B23" t="str">
-        <v>administration</v>
+        <v>/ədˌmɪnɪˈstreɪʃn/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>管理</v>
       </c>
-      <c r="D23" t="str">
-        <v>administration(管理)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>transportation</v>
       </c>
       <c r="B24" t="str">
-        <v>transportation</v>
+        <v>/ˌtrænspɔːrˈteɪʃn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>运输</v>
       </c>
-      <c r="D24" t="str">
-        <v>transportation(运输)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>aeroplane</v>
       </c>
       <c r="B25" t="str">
-        <v>aeroplane</v>
+        <v>/ˈerəpleɪn/</v>
       </c>
       <c r="C25" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>飞机</v>
       </c>
-      <c r="D25" t="str">
-        <v>aeroplane(飞机)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>spacecraft</v>
       </c>
       <c r="B26" t="str">
-        <v>spacecraft</v>
+        <v>/ˈspeɪskræft/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>宇宙飞船</v>
       </c>
-      <c r="D26" t="str">
-        <v>spacecraft(宇宙飞船)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>mechanical</v>
       </c>
       <c r="B27" t="str">
-        <v>mechanical</v>
+        <v>/məˈkænɪkl/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>机械的</v>
       </c>
-      <c r="D27" t="str">
-        <v>mechanical(机械的)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>rotary</v>
       </c>
       <c r="B28" t="str">
-        <v>rotary</v>
+        <v>/ˈroʊtəri/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>旋转的</v>
       </c>
-      <c r="D28" t="str">
-        <v>rotary(旋转的)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>woollen</v>
       </c>
       <c r="B29" t="str">
-        <v>woollen</v>
+        <v>/ˈwʊlən/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>羊毛制的</v>
       </c>
-      <c r="D29" t="str">
-        <v>woollen(羊毛制的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>willing</v>
       </c>
       <c r="B30" t="str">
-        <v>willing</v>
+        <v>/ˈwɪlɪŋ/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D30" t="str">
         <v>乐意的</v>
       </c>
-      <c r="D30" t="str">
-        <v>willing(乐意的)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>deceit</v>
       </c>
       <c r="B31" t="str">
-        <v>deceit</v>
+        <v>/dɪˈsiːt/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>欺骗</v>
       </c>
-      <c r="D31" t="str">
-        <v>deceit(欺骗)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>festival</v>
       </c>
       <c r="B32" t="str">
-        <v>festival</v>
+        <v>/ˈfestɪvl/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>节日</v>
       </c>
-      <c r="D32" t="str">
-        <v>festival(节日)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>bottom</v>
       </c>
       <c r="B33" t="str">
-        <v>cherry</v>
+        <v>/ˈbɑːtəm/</v>
       </c>
       <c r="C33" t="str">
-        <v>樱桃</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>cherry(樱桃)📢</v>
+        <v>底部</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>imply</v>
       </c>
       <c r="B34" t="str">
-        <v>bottom</v>
+        <v>/ɪmˈplaɪ/</v>
       </c>
       <c r="C34" t="str">
-        <v>底部</v>
+        <v>vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>bottom(底部)📢</v>
+        <v>暗示</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>interpret</v>
       </c>
       <c r="B35" t="str">
-        <v>imply</v>
+        <v>/ɪnˈtɜːrprət/</v>
       </c>
       <c r="C35" t="str">
-        <v>暗示</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>imply(暗示)📢</v>
+        <v>解释</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>style</v>
       </c>
       <c r="B36" t="str">
-        <v>interpret</v>
+        <v>/staɪl/</v>
       </c>
       <c r="C36" t="str">
-        <v>解释</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>interpret(解释)📢</v>
+        <v>风格</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>examination</v>
       </c>
       <c r="B37" t="str">
-        <v>willing</v>
+        <v>/ɪɡˌzæmɪˈneɪʃn/</v>
       </c>
       <c r="C37" t="str">
-        <v>乐意的</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>willing(乐意的)📢</v>
+        <v>检查</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>express</v>
       </c>
       <c r="B38" t="str">
-        <v>style</v>
+        <v>/ɪkˈspres/</v>
       </c>
       <c r="C38" t="str">
-        <v>风格</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D38" t="str">
-        <v>style(风格)📢</v>
+        <v>表达</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>environment</v>
       </c>
       <c r="B39" t="str">
-        <v>examination</v>
+        <v>/ɪnˈvaɪrənmənt/</v>
       </c>
       <c r="C39" t="str">
-        <v>检查</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>examination(检查)📢</v>
+        <v>环境</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>revolution</v>
       </c>
       <c r="B40" t="str">
-        <v>deceit</v>
+        <v>/ˌrevəˈluːʃn/</v>
       </c>
       <c r="C40" t="str">
-        <v>欺骗</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>deceit(欺骗)📢</v>
+        <v>革命</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>secondly</v>
       </c>
       <c r="B41" t="str">
-        <v>express</v>
+        <v>/ˈsekəndli/</v>
       </c>
       <c r="C41" t="str">
-        <v>表达</v>
+        <v>v./adv.</v>
       </c>
       <c r="D41" t="str">
-        <v>express(表达)📢</v>
+        <v>其次</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>shame</v>
       </c>
       <c r="B42" t="str">
-        <v>childhood</v>
+        <v>/ʃeɪm/</v>
       </c>
       <c r="C42" t="str">
-        <v>童年</v>
+        <v>n./vt.</v>
       </c>
       <c r="D42" t="str">
-        <v>childhood(童年)📢</v>
+        <v>羞耻</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>desperate</v>
       </c>
       <c r="B43" t="str">
-        <v>environment</v>
+        <v>/ˈdespərət/</v>
       </c>
       <c r="C43" t="str">
-        <v>环境</v>
+        <v>adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>environment(环境)📢</v>
+        <v>绝望的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>canon</v>
       </c>
       <c r="B44" t="str">
-        <v>revolution</v>
+        <v>/ˈkænən/</v>
       </c>
       <c r="C44" t="str">
-        <v>革命</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>revolution(革命)📢</v>
+        <v>标准</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>aim</v>
       </c>
       <c r="B45" t="str">
-        <v>festival</v>
+        <v>/eɪm/</v>
       </c>
       <c r="C45" t="str">
-        <v>节日</v>
+        <v>n./v.</v>
       </c>
       <c r="D45" t="str">
-        <v>festival(节日)📢</v>
+        <v>目标</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>settle</v>
       </c>
       <c r="B46" t="str">
-        <v>secondly</v>
+        <v>/ˈsetl/</v>
       </c>
       <c r="C46" t="str">
-        <v>其次</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>secondly(其次)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>shame</v>
-      </c>
-      <c r="C47" t="str">
-        <v>羞耻</v>
-      </c>
-      <c r="D47" t="str">
-        <v>shame(羞耻)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>desperate</v>
-      </c>
-      <c r="C48" t="str">
-        <v>绝望的</v>
-      </c>
-      <c r="D48" t="str">
-        <v>desperate(绝望的)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>middle</v>
-      </c>
-      <c r="C49" t="str">
-        <v>中间</v>
-      </c>
-      <c r="D49" t="str">
-        <v>middle(中间)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>angry</v>
-      </c>
-      <c r="C50" t="str">
-        <v>生气的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>angry(生气的)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>canon</v>
-      </c>
-      <c r="C51" t="str">
-        <v>标准</v>
-      </c>
-      <c r="D51" t="str">
-        <v>canon(标准)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>bottom</v>
-      </c>
-      <c r="C52" t="str">
-        <v>底部</v>
-      </c>
-      <c r="D52" t="str">
-        <v>bottom(底部)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>desperate</v>
-      </c>
-      <c r="C53" t="str">
-        <v>绝望的</v>
-      </c>
-      <c r="D53" t="str">
-        <v>desperate(绝望的)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>aim</v>
-      </c>
-      <c r="C54" t="str">
-        <v>目标</v>
-      </c>
-      <c r="D54" t="str">
-        <v>aim(目标)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>environment</v>
-      </c>
-      <c r="C55" t="str">
-        <v>环境</v>
-      </c>
-      <c r="D55" t="str">
-        <v>environment(环境)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>settle</v>
-      </c>
-      <c r="C56" t="str">
         <v>解决</v>
-      </c>
-      <c r="D56" t="str">
-        <v>settle(解决)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D46"/>
   </ignoredErrors>
 </worksheet>
 </file>